--- a/forms/trg/Formulir_TRG_hvit-rg.xlsx
+++ b/forms/trg/Formulir_TRG_hvit-rg.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B22)</f>
+        <f>COUNTA(Anggota!B5:B23)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F22)</f>
+        <f>COUNTA(Anggota!F5:F23)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,22 +913,22 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Ir. Ian Adrian Bustanuddin, S.T., M.T</t>
+          <t>Prof. Dr. Ir. Salama Manjang, MT., IPU., ASEAN Eng.</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Power Systems &amp; Computational</t>
+          <t>Department of Electrical Engineering, Hasanuddin University</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Department of Electrical Engineering, Hasanuddin University</t>
+          <t>high voltage and insulation</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -937,15 +937,19 @@
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>0009-0005-5908-6966</t>
+          <t>0000-0001-9616-7435</t>
         </is>
       </c>
       <c r="K5" s="11" t="inlineStr">
         <is>
-          <t>6924668</t>
-        </is>
-      </c>
-      <c r="L5" s="12" t="n"/>
+          <t>5990308</t>
+        </is>
+      </c>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>59754835800</t>
+        </is>
+      </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -958,22 +962,22 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Dr.Eng. Lukmanul Hakim Arma, ST.MT</t>
+          <t>Ir. Ian Adrian Bustanuddin, S.T., M.T</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Metalurgi Engineering</t>
+          <t>Power Systems &amp; Computational</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Department of Mechanical Engineering, Hasanuddin University</t>
+          <t>Department of Electrical Engineering, Hasanuddin University</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -982,12 +986,12 @@
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>0009-0002-2502-4191</t>
+          <t>0009-0005-5908-6966</t>
         </is>
       </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
-          <t>6659783</t>
+          <t>6924668</t>
         </is>
       </c>
       <c r="L6" s="12" t="n"/>
@@ -1003,22 +1007,22 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr.-Ing. Ir. Faizal Arya Samman</t>
+          <t>Dr.Eng. Lukmanul Hakim Arma, ST.MT</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Power Electronics</t>
+          <t>Metalurgi Engineering</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Department of Electrical Engineering, Hasanuddin University</t>
+          <t>Department of Mechanical Engineering, Hasanuddin University</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1027,19 +1031,15 @@
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-1985-5805</t>
+          <t>0009-0002-2502-4191</t>
         </is>
       </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
-          <t>6005320</t>
-        </is>
-      </c>
-      <c r="L7" s="11" t="inlineStr">
-        <is>
-          <t>24587976100</t>
-        </is>
-      </c>
+          <t>6659783</t>
+        </is>
+      </c>
+      <c r="L7" s="12" t="n"/>
       <c r="M7" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1052,17 +1052,17 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ikhlas Kitta, ST, MT</t>
+          <t>Prof. Dr.-Ing. Ir. Faizal Arya Samman</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>High Voltage Transmission</t>
+          <t>Power Electronics</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -1076,17 +1076,17 @@
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-6991-0342</t>
+          <t>0000-0002-1985-5805</t>
         </is>
       </c>
       <c r="K8" s="11" t="inlineStr">
         <is>
-          <t>5992714</t>
+          <t>6005320</t>
         </is>
       </c>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>57204926498</t>
+          <t>24587976100</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1101,22 +1101,22 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Prof. Ir. Dr. Hazlie Bin Mokhlis</t>
+          <t>Dr. Ikhlas Kitta, ST, MT</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Electrical Power System &amp; Control Optimization Algoritthm</t>
+          <t>High Voltage Transmission</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Department of Electrical Engineering, Universiti Malaya</t>
+          <t>Department of Electrical Engineering, Hasanuddin University</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1125,13 +1125,17 @@
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-1166-1934</t>
-        </is>
-      </c>
-      <c r="K9" s="12" t="n"/>
+          <t>0000-0001-6991-0342</t>
+        </is>
+      </c>
+      <c r="K9" s="11" t="inlineStr">
+        <is>
+          <t>5992714</t>
+        </is>
+      </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>8136874200</t>
+          <t>57204926498</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1146,22 +1150,22 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ir. Mustamin, S.T., M.T.</t>
+          <t>Prof. Ir. Dr. Hazlie Bin Mokhlis</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Power Installation Materials</t>
+          <t>Electrical Power System &amp; Control Optimization Algoritthm</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Department of Electrical Engineering, Halu Oleo University</t>
+          <t>Department of Electrical Engineering, Universiti Malaya</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1170,15 +1174,15 @@
       <c r="I10" s="12" t="n"/>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-7691-4496</t>
-        </is>
-      </c>
-      <c r="K10" s="11" t="inlineStr">
-        <is>
-          <t>6002720</t>
-        </is>
-      </c>
-      <c r="L10" s="12" t="n"/>
+          <t>0000-0002-1166-1934</t>
+        </is>
+      </c>
+      <c r="K10" s="12" t="n"/>
+      <c r="L10" s="11" t="inlineStr">
+        <is>
+          <t>8136874200</t>
+        </is>
+      </c>
       <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1189,18 +1193,46 @@
       <c r="A11" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="11" t="n"/>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Dr. Ir. Mustamin, S.T., M.T.</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Power Installation Materials</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Department of Electrical Engineering, Halu Oleo University</t>
+        </is>
+      </c>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
       <c r="I11" s="12" t="n"/>
-      <c r="J11" s="12" t="n"/>
-      <c r="K11" s="12" t="n"/>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-7691-4496</t>
+        </is>
+      </c>
+      <c r="K11" s="11" t="inlineStr">
+        <is>
+          <t>6002720</t>
+        </is>
+      </c>
       <c r="L11" s="12" t="n"/>
-      <c r="M11" s="12" t="n"/>
+      <c r="M11" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -1389,15 +1421,32 @@
       <c r="L22" s="12" t="n"/>
       <c r="M22" s="12" t="n"/>
     </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="12" t="n"/>
+      <c r="C23" s="12" t="n"/>
+      <c r="D23" s="12" t="n"/>
+      <c r="E23" s="11" t="n"/>
+      <c r="F23" s="12" t="n"/>
+      <c r="G23" s="12" t="n"/>
+      <c r="H23" s="12" t="n"/>
+      <c r="I23" s="12" t="n"/>
+      <c r="J23" s="12" t="n"/>
+      <c r="K23" s="12" t="n"/>
+      <c r="L23" s="12" t="n"/>
+      <c r="M23" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
